--- a/business_forms/033_financial_planner_recommendation_form--business_forms.xlsx
+++ b/business_forms/033_financial_planner_recommendation_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'self_employed'}</t>
+          <t>self employed</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'business'}</t>
+          <t>business</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'investments'}</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'investments'}</t>
+          <t>investments</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'medium_high'}</t>
+          <t>medium_high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'medium_high'}</t>
+          <t>medium high</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'high_high'}</t>
+          <t>high_high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'high_high'}</t>
+          <t>high high</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'short_term'}</t>
+          <t>short_term</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'short_term'}</t>
+          <t>short term</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'long_term'}</t>
+          <t>long_term</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'long_term'}</t>
+          <t>long term</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'medium_term'}</t>
+          <t>medium_term</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'medium_term'}</t>
+          <t>medium term</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'infrequent'}</t>
+          <t>infrequent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'infrequent'}</t>
+          <t>infrequent</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'frequent'}</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'frequent'}</t>
+          <t>frequent</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'very_frequent'}</t>
+          <t>very_frequent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'very_frequent'}</t>
+          <t>very frequent</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'financial_advisor'}</t>
+          <t>financial_advisor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'financial_advisor'}</t>
+          <t>financial advisor</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'financial_planner'}</t>
+          <t>financial_planner</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'financial_planner'}</t>
+          <t>financial planner</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'planner_advisor'}</t>
+          <t>planner_advisor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'planner_advisor'}</t>
+          <t>planner advisor</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'fidelity'}</t>
+          <t>fidelity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'fidelity'}</t>
+          <t>fidelity</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'charles_schwab'}</t>
+          <t>charles_schwab</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'charles_schwab'}</t>
+          <t>charles schwab</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'t_d_apex'}</t>
+          <t>t_d_apex</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 't_d_apex'}</t>
+          <t>t d apex</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'joint'}</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'joint'}</t>
+          <t>joint</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'trust'}</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'trust'}</t>
+          <t>trust</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>investment_investor_status_choices</t>
+          <t>account_type_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>individual</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'individual'}</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'individual'}</t>
+          <t>joint</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'joint'}</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'joint'}</t>
+          <t>trust</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>account_status_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'trust'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'trust'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1845,46 +1845,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'active'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>account_status_choices</t>
+          <t>account_investor_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>individual</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>account_status_choices</t>
+          <t>account_investor_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>joint</t>
         </is>
       </c>
     </row>
@@ -1896,97 +1896,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'individual'}</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'individual'}</t>
+          <t>trust</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>account_investor_choices</t>
+          <t>account_investor_type_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'joint'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'joint'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>account_investor_choices</t>
+          <t>account_investor_type_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'trust'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'trust'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>account_investor_type_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'value':_'active'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'value': 'active'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>account_investor_type_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'value':_'inactive'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'value': 'inactive'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>account_investor_type_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'value':_'inactive'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
